--- a/app/reports/REGN_research.xlsx
+++ b/app/reports/REGN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.635</v>
+        <v>0.643</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>864.83</v>
+        <v>874.27</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>762.46</v>
+        <v>758.78</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.134</v>
+        <v>0.152</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.795</v>
+        <v>0.799</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.634</v>
+        <v>0.652</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04690000057220459</v>
+        <v>0.0463100004196167</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>102954990.1109566</v>
+        <v>102954993.4790058</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>762.46</v>
+        <v>758.78</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>78499061760</v>
+        <v>78120189952</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>18.86</v>
+        <v>18.79</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>15.07</v>
+        <v>15</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>28966998016</v>
+        <v>29158010880</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>37.780106</v>
+        <v>35.432114</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>25.774</v>
+        <v>27.653</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>5.658</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>51574185984</v>
+        <v>52384178176</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>31.64174</v>
+        <v>32.089714</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>824.456</v>
+        <v>802.1319999999999</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>250.169</v>
+        <v>243.395</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>74706067456</v>
+        <v>72764850176</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>11.687474</v>
+        <v>11.393198</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>7.732</v>
+        <v>7.795</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>60456927232</v>
+        <v>59833360384</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>23.81111</v>
+        <v>23.802631</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>13.9</v>
+        <v>13.791</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.224</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>82339848192</v>
+        <v>82716114944</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>16.777508</v>
+        <v>16.861626</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>9.031000000000001</v>
+        <v>9.212</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.374</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="11">
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>17506381824</v>
+        <v>17819488256</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>21.767176</v>
+        <v>22.156488</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>16.201</v>
+        <v>16.113</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>5.524</v>
+        <v>5.494</v>
       </c>
     </row>
     <row r="12">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>45224411136</v>
+        <v>47123914752</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>42.186165</v>
+        <v>43.958057</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>29.113</v>
+        <v>29.561</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>10.123</v>
+        <v>10.278</v>
       </c>
     </row>
     <row r="13">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>24054648832</v>
+        <v>24293324800</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>15.1175165</v>
+        <v>15.404883</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>10.157</v>
+        <v>10.044</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>3.39</v>
+        <v>3.352</v>
       </c>
     </row>
     <row r="15">
